--- a/small_business_tracker_template.xlsx
+++ b/small_business_tracker_template.xlsx
@@ -434,7 +434,7 @@
     <numFmt numFmtId="167" formatCode="mm/dd/yyyy"/>
     <numFmt numFmtId="168" formatCode="0"/>
   </numFmts>
-  <fonts count="18">
+  <fonts count="21">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -535,8 +535,32 @@
     </font>
     <font>
       <b val="true"/>
+      <sz val="13"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Arial"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <i val="true"/>
+      <sz val="12"/>
+      <color rgb="FFC9DFC2"/>
+      <name val="Arial"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <b val="true"/>
       <sz val="9"/>
-      <color rgb="FFFFFFFF"/>
+      <color rgb="FF1F3B21"/>
+      <name val="Arial"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <b val="true"/>
+      <sz val="16"/>
+      <color rgb="FF1F3B21"/>
       <name val="Arial"/>
       <family val="0"/>
       <charset val="1"/>
@@ -562,7 +586,7 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -572,7 +596,7 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF2F5233"/>
-        <bgColor rgb="FF555555"/>
+        <bgColor rgb="FF1F3B21"/>
       </patternFill>
     </fill>
     <fill>
@@ -583,18 +607,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF4C7A47"/>
-        <bgColor rgb="FF555555"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEFF5EC"/>
-        <bgColor rgb="FFEAF7EC"/>
+        <fgColor rgb="FFDCEAD5"/>
+        <bgColor rgb="FFD9D9D9"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border diagonalUp="false" diagonalDown="false">
       <left/>
       <right/>
@@ -614,6 +632,15 @@
       </top>
       <bottom style="thin">
         <color rgb="FFCCCCCC"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border diagonalUp="false" diagonalDown="false">
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FF2F5233"/>
       </bottom>
       <diagonal/>
     </border>
@@ -643,7 +670,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="27">
+  <cellXfs count="32">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -728,23 +755,43 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="14" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="14" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="15" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="16" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="168" fontId="13" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="4" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="168" fontId="17" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="13" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="166" fontId="17" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="2" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="10" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="166" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="13" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="17" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -819,13 +866,13 @@
       <rgbColor rgb="FF008080"/>
       <rgbColor rgb="FF0000FF"/>
       <rgbColor rgb="FF00CCFF"/>
-      <rgbColor rgb="FFEFF5EC"/>
-      <rgbColor rgb="FFCCFFCC"/>
       <rgbColor rgb="FFFDEEEE"/>
+      <rgbColor rgb="FFDCEAD5"/>
+      <rgbColor rgb="FFFFFF99"/>
       <rgbColor rgb="FF99CCFF"/>
       <rgbColor rgb="FFFF99CC"/>
       <rgbColor rgb="FFCC99FF"/>
-      <rgbColor rgb="FFFFCC99"/>
+      <rgbColor rgb="FFC9DFC2"/>
       <rgbColor rgb="FF4F81BD"/>
       <rgbColor rgb="FF4BACC6"/>
       <rgbColor rgb="FF9BBB59"/>
@@ -835,13 +882,13 @@
       <rgbColor rgb="FF8064A2"/>
       <rgbColor rgb="FF888888"/>
       <rgbColor rgb="FF003366"/>
-      <rgbColor rgb="FF4C7A47"/>
+      <rgbColor rgb="FF339966"/>
       <rgbColor rgb="FF003300"/>
-      <rgbColor rgb="FF333300"/>
+      <rgbColor rgb="FF2F5233"/>
       <rgbColor rgb="FF993300"/>
       <rgbColor rgb="FF993366"/>
       <rgbColor rgb="FF555555"/>
-      <rgbColor rgb="FF2F5233"/>
+      <rgbColor rgb="FF1F3B21"/>
     </indexedColors>
   </colors>
 </styleSheet>
@@ -975,12 +1022,13 @@
                 </a:p>
               </c:txPr>
               <c:dLblPos val="bestFit"/>
-              <c:showLegendKey val="1"/>
-              <c:showVal val="1"/>
-              <c:showCatName val="1"/>
-              <c:showSerName val="1"/>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="0"/>
+              <c:showCatName val="0"/>
+              <c:showSerName val="0"/>
               <c:showPercent val="1"/>
-              <c:separator>; </c:separator>
+              <c:separator>
+</c:separator>
             </c:dLbl>
             <c:dLbl>
               <c:idx val="1"/>
@@ -999,12 +1047,13 @@
                 </a:p>
               </c:txPr>
               <c:dLblPos val="bestFit"/>
-              <c:showLegendKey val="1"/>
-              <c:showVal val="1"/>
-              <c:showCatName val="1"/>
-              <c:showSerName val="1"/>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="0"/>
+              <c:showCatName val="0"/>
+              <c:showSerName val="0"/>
               <c:showPercent val="1"/>
-              <c:separator>; </c:separator>
+              <c:separator>
+</c:separator>
             </c:dLbl>
             <c:dLbl>
               <c:idx val="2"/>
@@ -1023,12 +1072,13 @@
                 </a:p>
               </c:txPr>
               <c:dLblPos val="bestFit"/>
-              <c:showLegendKey val="1"/>
-              <c:showVal val="1"/>
-              <c:showCatName val="1"/>
-              <c:showSerName val="1"/>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="0"/>
+              <c:showCatName val="0"/>
+              <c:showSerName val="0"/>
               <c:showPercent val="1"/>
-              <c:separator>; </c:separator>
+              <c:separator>
+</c:separator>
             </c:dLbl>
             <c:dLbl>
               <c:idx val="3"/>
@@ -1047,12 +1097,13 @@
                 </a:p>
               </c:txPr>
               <c:dLblPos val="bestFit"/>
-              <c:showLegendKey val="1"/>
-              <c:showVal val="1"/>
-              <c:showCatName val="1"/>
-              <c:showSerName val="1"/>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="0"/>
+              <c:showCatName val="0"/>
+              <c:showSerName val="0"/>
               <c:showPercent val="1"/>
-              <c:separator>; </c:separator>
+              <c:separator>
+</c:separator>
             </c:dLbl>
             <c:dLbl>
               <c:idx val="4"/>
@@ -1071,12 +1122,13 @@
                 </a:p>
               </c:txPr>
               <c:dLblPos val="bestFit"/>
-              <c:showLegendKey val="1"/>
-              <c:showVal val="1"/>
-              <c:showCatName val="1"/>
-              <c:showSerName val="1"/>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="0"/>
+              <c:showCatName val="0"/>
+              <c:showSerName val="0"/>
               <c:showPercent val="1"/>
-              <c:separator>; </c:separator>
+              <c:separator>
+</c:separator>
             </c:dLbl>
             <c:txPr>
               <a:bodyPr wrap="square"/>
@@ -1093,12 +1145,13 @@
               </a:p>
             </c:txPr>
             <c:dLblPos val="bestFit"/>
-            <c:showLegendKey val="1"/>
-            <c:showVal val="1"/>
-            <c:showCatName val="1"/>
-            <c:showSerName val="1"/>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="0"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
             <c:showPercent val="1"/>
-            <c:separator>; </c:separator>
+            <c:separator>
+</c:separator>
             <c:showLeaderLines val="1"/>
           </c:dLbls>
           <c:cat>
@@ -1260,10 +1313,12 @@
           </c:tx>
           <c:spPr>
             <a:solidFill>
-              <a:srgbClr val="4f81bd"/>
+              <a:srgbClr val="2f5233"/>
             </a:solidFill>
             <a:ln w="0">
-              <a:noFill/>
+              <a:solidFill>
+                <a:srgbClr val="2f5233"/>
+              </a:solidFill>
             </a:ln>
           </c:spPr>
           <c:invertIfNegative val="0"/>
@@ -1384,11 +1439,11 @@
         </c:ser>
         <c:gapWidth val="150"/>
         <c:overlap val="0"/>
-        <c:axId val="51413403"/>
-        <c:axId val="94388029"/>
+        <c:axId val="80368281"/>
+        <c:axId val="95250689"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="51413403"/>
+        <c:axId val="80368281"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1420,7 +1475,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="94388029"/>
+        <c:crossAx val="95250689"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -1428,7 +1483,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="94388029"/>
+        <c:axId val="95250689"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1504,7 +1559,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="51413403"/>
+        <c:crossAx val="80368281"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -1617,10 +1672,12 @@
           </c:tx>
           <c:spPr>
             <a:solidFill>
-              <a:srgbClr val="4f81bd"/>
+              <a:srgbClr val="2f5233"/>
             </a:solidFill>
             <a:ln w="0">
-              <a:noFill/>
+              <a:solidFill>
+                <a:srgbClr val="2f5233"/>
+              </a:solidFill>
             </a:ln>
           </c:spPr>
           <c:invertIfNegative val="0"/>
@@ -1684,11 +1741,11 @@
         </c:ser>
         <c:gapWidth val="150"/>
         <c:overlap val="0"/>
-        <c:axId val="93748083"/>
-        <c:axId val="68863794"/>
+        <c:axId val="90601526"/>
+        <c:axId val="13102782"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="93748083"/>
+        <c:axId val="90601526"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1720,7 +1777,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="68863794"/>
+        <c:crossAx val="13102782"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -1728,7 +1785,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="68863794"/>
+        <c:axId val="13102782"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1804,7 +1861,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="93748083"/>
+        <c:crossAx val="90601526"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -1917,10 +1974,12 @@
           </c:tx>
           <c:spPr>
             <a:solidFill>
-              <a:srgbClr val="4f81bd"/>
+              <a:srgbClr val="2f5233"/>
             </a:solidFill>
             <a:ln w="0">
-              <a:noFill/>
+              <a:solidFill>
+                <a:srgbClr val="2f5233"/>
+              </a:solidFill>
             </a:ln>
           </c:spPr>
           <c:invertIfNegative val="0"/>
@@ -1999,11 +2058,11 @@
         </c:ser>
         <c:gapWidth val="150"/>
         <c:overlap val="0"/>
-        <c:axId val="54012335"/>
-        <c:axId val="68109484"/>
+        <c:axId val="4596900"/>
+        <c:axId val="94623711"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="54012335"/>
+        <c:axId val="4596900"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2035,7 +2094,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="68109484"/>
+        <c:crossAx val="94623711"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -2043,7 +2102,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="68109484"/>
+        <c:axId val="94623711"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2119,7 +2178,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="54012335"/>
+        <c:crossAx val="4596900"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -2177,14 +2236,14 @@
     <xdr:from>
       <xdr:col>3</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>7</xdr:row>
-      <xdr:rowOff>176040</xdr:rowOff>
+      <xdr:row>8</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>6</xdr:col>
       <xdr:colOff>659520</xdr:colOff>
       <xdr:row>22</xdr:row>
-      <xdr:rowOff>18000</xdr:rowOff>
+      <xdr:rowOff>32400</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame>
       <xdr:nvGraphicFramePr>
@@ -2192,7 +2251,7 @@
         <xdr:cNvGraphicFramePr/>
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
-        <a:off x="4267080" y="1800360"/>
+        <a:off x="4267080" y="2104920"/>
         <a:ext cx="3599640" cy="2699640"/>
       </xdr:xfrm>
       <a:graphic>
@@ -2207,14 +2266,14 @@
     <xdr:from>
       <xdr:col>3</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>16</xdr:row>
-      <xdr:rowOff>175680</xdr:rowOff>
+      <xdr:row>17</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>9</xdr:col>
       <xdr:colOff>542880</xdr:colOff>
       <xdr:row>31</xdr:row>
-      <xdr:rowOff>18000</xdr:rowOff>
+      <xdr:rowOff>32760</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame>
       <xdr:nvGraphicFramePr>
@@ -2222,7 +2281,7 @@
         <xdr:cNvGraphicFramePr/>
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
-        <a:off x="4267080" y="3514680"/>
+        <a:off x="4267080" y="3819600"/>
         <a:ext cx="5759640" cy="2699640"/>
       </xdr:xfrm>
       <a:graphic>
@@ -2237,14 +2296,14 @@
     <xdr:from>
       <xdr:col>4</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>32</xdr:row>
-      <xdr:rowOff>176040</xdr:rowOff>
+      <xdr:row>33</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>10</xdr:col>
       <xdr:colOff>486360</xdr:colOff>
       <xdr:row>47</xdr:row>
-      <xdr:rowOff>18000</xdr:rowOff>
+      <xdr:rowOff>32400</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame>
       <xdr:nvGraphicFramePr>
@@ -2252,7 +2311,7 @@
         <xdr:cNvGraphicFramePr/>
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
-        <a:off x="5689440" y="6562800"/>
+        <a:off x="5689440" y="6867360"/>
         <a:ext cx="5039640" cy="2699640"/>
       </xdr:xfrm>
       <a:graphic>
@@ -2272,14 +2331,14 @@
     <xdr:from>
       <xdr:col>5</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>7</xdr:row>
-      <xdr:rowOff>176040</xdr:rowOff>
+      <xdr:row>8</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>12</xdr:col>
       <xdr:colOff>447840</xdr:colOff>
       <xdr:row>22</xdr:row>
-      <xdr:rowOff>18000</xdr:rowOff>
+      <xdr:rowOff>32400</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame>
       <xdr:nvGraphicFramePr>
@@ -2287,7 +2346,7 @@
         <xdr:cNvGraphicFramePr/>
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
-        <a:off x="7159680" y="1828800"/>
+        <a:off x="7159680" y="2104920"/>
         <a:ext cx="5759640" cy="2699640"/>
       </xdr:xfrm>
       <a:graphic>
@@ -9786,61 +9845,69 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="1" style="0" width="16"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
+    <row r="1" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A1" s="21" t="s">
         <v>87</v>
       </c>
-      <c r="B1" s="1"/>
-      <c r="C1" s="1"/>
-      <c r="D1" s="1"/>
-      <c r="E1" s="1"/>
-      <c r="F1" s="1"/>
-      <c r="G1" s="1"/>
-      <c r="H1" s="1"/>
-    </row>
-    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="4" t="s">
+      <c r="B1" s="21"/>
+      <c r="C1" s="21"/>
+      <c r="D1" s="21"/>
+      <c r="E1" s="21"/>
+      <c r="F1" s="21"/>
+      <c r="G1" s="21"/>
+      <c r="H1" s="21"/>
+    </row>
+    <row r="2" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A2" s="22" t="s">
         <v>88</v>
       </c>
-      <c r="B2" s="4"/>
-      <c r="C2" s="4"/>
-      <c r="D2" s="4"/>
-      <c r="E2" s="4"/>
-      <c r="F2" s="4"/>
-      <c r="G2" s="4"/>
-      <c r="H2" s="4"/>
-    </row>
-    <row r="5" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="21" t="s">
+      <c r="B2" s="22"/>
+      <c r="C2" s="22"/>
+      <c r="D2" s="22"/>
+      <c r="E2" s="22"/>
+      <c r="F2" s="22"/>
+      <c r="G2" s="22"/>
+      <c r="H2" s="22"/>
+    </row>
+    <row r="5" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A5" s="23" t="s">
         <v>42</v>
       </c>
-      <c r="B5" s="21" t="s">
+      <c r="B5" s="23" t="s">
         <v>89</v>
       </c>
-      <c r="C5" s="21" t="s">
+      <c r="C5" s="23" t="s">
         <v>90</v>
       </c>
-      <c r="D5" s="21" t="s">
+      <c r="D5" s="23" t="s">
         <v>91</v>
       </c>
-    </row>
-    <row r="6" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="22" t="n">
+      <c r="E5" s="24"/>
+      <c r="F5" s="24"/>
+      <c r="G5" s="24"/>
+      <c r="H5" s="24"/>
+    </row>
+    <row r="6" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A6" s="25" t="n">
         <f aca="false">SUMPRODUCT(('Order Tracker'!$B$3:$B$102=1)*1)</f>
         <v>0</v>
       </c>
-      <c r="B6" s="23" t="n">
+      <c r="B6" s="26" t="n">
         <f aca="false">SUM('Order Tracker'!$I$3:$I$102)</f>
         <v>0</v>
       </c>
-      <c r="C6" s="22" t="n">
+      <c r="C6" s="25" t="n">
         <f aca="false">COUNTA('Customer Tracker'!$B$3:$B$52)</f>
         <v>0</v>
       </c>
-      <c r="D6" s="23" t="n">
+      <c r="D6" s="26" t="n">
         <f aca="false">IFERROR(B6/A6,0)</f>
         <v>0</v>
       </c>
+      <c r="E6" s="24"/>
+      <c r="F6" s="24"/>
+      <c r="G6" s="24"/>
+      <c r="H6" s="24"/>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="6" t="s">
@@ -9848,10 +9915,10 @@
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="10" t="s">
+      <c r="A10" s="27" t="s">
         <v>58</v>
       </c>
-      <c r="B10" s="10" t="s">
+      <c r="B10" s="27" t="s">
         <v>93</v>
       </c>
     </row>
@@ -9907,15 +9974,15 @@
       <c r="C18" s="6" t="s">
         <v>74</v>
       </c>
-      <c r="D18" s="15" t="n">
+      <c r="D18" s="28" t="n">
         <v>2026</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="10" t="s">
+      <c r="A19" s="27" t="s">
         <v>75</v>
       </c>
-      <c r="B19" s="10" t="s">
+      <c r="B19" s="27" t="s">
         <v>95</v>
       </c>
     </row>
@@ -9923,7 +9990,7 @@
       <c r="A20" s="9" t="s">
         <v>96</v>
       </c>
-      <c r="B20" s="24" t="n">
+      <c r="B20" s="29" t="n">
         <f aca="false">SUMIFS('Order Tracker'!$I$3:$I$102,'Order Tracker'!$L$3:$L$102,$D$18,'Order Tracker'!$M$3:$M$102,1)</f>
         <v>0</v>
       </c>
@@ -9932,7 +9999,7 @@
       <c r="A21" s="9" t="s">
         <v>97</v>
       </c>
-      <c r="B21" s="24" t="n">
+      <c r="B21" s="29" t="n">
         <f aca="false">SUMIFS('Order Tracker'!$I$3:$I$102,'Order Tracker'!$L$3:$L$102,$D$18,'Order Tracker'!$M$3:$M$102,2)</f>
         <v>0</v>
       </c>
@@ -9941,7 +10008,7 @@
       <c r="A22" s="9" t="s">
         <v>98</v>
       </c>
-      <c r="B22" s="24" t="n">
+      <c r="B22" s="29" t="n">
         <f aca="false">SUMIFS('Order Tracker'!$I$3:$I$102,'Order Tracker'!$L$3:$L$102,$D$18,'Order Tracker'!$M$3:$M$102,3)</f>
         <v>0</v>
       </c>
@@ -9950,7 +10017,7 @@
       <c r="A23" s="9" t="s">
         <v>99</v>
       </c>
-      <c r="B23" s="24" t="n">
+      <c r="B23" s="29" t="n">
         <f aca="false">SUMIFS('Order Tracker'!$I$3:$I$102,'Order Tracker'!$L$3:$L$102,$D$18,'Order Tracker'!$M$3:$M$102,4)</f>
         <v>0</v>
       </c>
@@ -9959,7 +10026,7 @@
       <c r="A24" s="9" t="s">
         <v>100</v>
       </c>
-      <c r="B24" s="24" t="n">
+      <c r="B24" s="29" t="n">
         <f aca="false">SUMIFS('Order Tracker'!$I$3:$I$102,'Order Tracker'!$L$3:$L$102,$D$18,'Order Tracker'!$M$3:$M$102,5)</f>
         <v>0</v>
       </c>
@@ -9968,7 +10035,7 @@
       <c r="A25" s="9" t="s">
         <v>101</v>
       </c>
-      <c r="B25" s="24" t="n">
+      <c r="B25" s="29" t="n">
         <f aca="false">SUMIFS('Order Tracker'!$I$3:$I$102,'Order Tracker'!$L$3:$L$102,$D$18,'Order Tracker'!$M$3:$M$102,6)</f>
         <v>0</v>
       </c>
@@ -9977,7 +10044,7 @@
       <c r="A26" s="9" t="s">
         <v>102</v>
       </c>
-      <c r="B26" s="24" t="n">
+      <c r="B26" s="29" t="n">
         <f aca="false">SUMIFS('Order Tracker'!$I$3:$I$102,'Order Tracker'!$L$3:$L$102,$D$18,'Order Tracker'!$M$3:$M$102,7)</f>
         <v>0</v>
       </c>
@@ -9986,7 +10053,7 @@
       <c r="A27" s="9" t="s">
         <v>103</v>
       </c>
-      <c r="B27" s="24" t="n">
+      <c r="B27" s="29" t="n">
         <f aca="false">SUMIFS('Order Tracker'!$I$3:$I$102,'Order Tracker'!$L$3:$L$102,$D$18,'Order Tracker'!$M$3:$M$102,8)</f>
         <v>0</v>
       </c>
@@ -9995,7 +10062,7 @@
       <c r="A28" s="9" t="s">
         <v>104</v>
       </c>
-      <c r="B28" s="24" t="n">
+      <c r="B28" s="29" t="n">
         <f aca="false">SUMIFS('Order Tracker'!$I$3:$I$102,'Order Tracker'!$L$3:$L$102,$D$18,'Order Tracker'!$M$3:$M$102,9)</f>
         <v>0</v>
       </c>
@@ -10004,7 +10071,7 @@
       <c r="A29" s="9" t="s">
         <v>105</v>
       </c>
-      <c r="B29" s="24" t="n">
+      <c r="B29" s="29" t="n">
         <f aca="false">SUMIFS('Order Tracker'!$I$3:$I$102,'Order Tracker'!$L$3:$L$102,$D$18,'Order Tracker'!$M$3:$M$102,10)</f>
         <v>0</v>
       </c>
@@ -10013,7 +10080,7 @@
       <c r="A30" s="9" t="s">
         <v>106</v>
       </c>
-      <c r="B30" s="24" t="n">
+      <c r="B30" s="29" t="n">
         <f aca="false">SUMIFS('Order Tracker'!$I$3:$I$102,'Order Tracker'!$L$3:$L$102,$D$18,'Order Tracker'!$M$3:$M$102,11)</f>
         <v>0</v>
       </c>
@@ -10022,7 +10089,7 @@
       <c r="A31" s="9" t="s">
         <v>107</v>
       </c>
-      <c r="B31" s="24" t="n">
+      <c r="B31" s="29" t="n">
         <f aca="false">SUMIFS('Order Tracker'!$I$3:$I$102,'Order Tracker'!$L$3:$L$102,$D$18,'Order Tracker'!$M$3:$M$102,12)</f>
         <v>0</v>
       </c>
@@ -10033,13 +10100,13 @@
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A35" s="10" t="s">
+      <c r="A35" s="27" t="s">
         <v>109</v>
       </c>
-      <c r="B35" s="10" t="s">
+      <c r="B35" s="27" t="s">
         <v>68</v>
       </c>
-      <c r="C35" s="10" t="s">
+      <c r="C35" s="27" t="s">
         <v>95</v>
       </c>
     </row>
@@ -10051,7 +10118,7 @@
         <f aca="false">IFERROR(INDEX('Inventory Tracker'!$B$3:$B$52,MATCH(1,'Inventory Tracker'!$M$3:$M$52,0)),"")</f>
         <v/>
       </c>
-      <c r="C36" s="24" t="str">
+      <c r="C36" s="29" t="str">
         <f aca="false">IFERROR(INDEX('Inventory Tracker'!$L$3:$L$52,MATCH(1,'Inventory Tracker'!$M$3:$M$52,0)),"")</f>
         <v/>
       </c>
@@ -10064,7 +10131,7 @@
         <f aca="false">IFERROR(INDEX('Inventory Tracker'!$B$3:$B$52,MATCH(2,'Inventory Tracker'!$M$3:$M$52,0)),"")</f>
         <v/>
       </c>
-      <c r="C37" s="24" t="str">
+      <c r="C37" s="29" t="str">
         <f aca="false">IFERROR(INDEX('Inventory Tracker'!$L$3:$L$52,MATCH(2,'Inventory Tracker'!$M$3:$M$52,0)),"")</f>
         <v/>
       </c>
@@ -10077,7 +10144,7 @@
         <f aca="false">IFERROR(INDEX('Inventory Tracker'!$B$3:$B$52,MATCH(3,'Inventory Tracker'!$M$3:$M$52,0)),"")</f>
         <v/>
       </c>
-      <c r="C38" s="24" t="str">
+      <c r="C38" s="29" t="str">
         <f aca="false">IFERROR(INDEX('Inventory Tracker'!$L$3:$L$52,MATCH(3,'Inventory Tracker'!$M$3:$M$52,0)),"")</f>
         <v/>
       </c>
@@ -10090,7 +10157,7 @@
         <f aca="false">IFERROR(INDEX('Inventory Tracker'!$B$3:$B$52,MATCH(4,'Inventory Tracker'!$M$3:$M$52,0)),"")</f>
         <v/>
       </c>
-      <c r="C39" s="24" t="str">
+      <c r="C39" s="29" t="str">
         <f aca="false">IFERROR(INDEX('Inventory Tracker'!$L$3:$L$52,MATCH(4,'Inventory Tracker'!$M$3:$M$52,0)),"")</f>
         <v/>
       </c>
@@ -10103,7 +10170,7 @@
         <f aca="false">IFERROR(INDEX('Inventory Tracker'!$B$3:$B$52,MATCH(5,'Inventory Tracker'!$M$3:$M$52,0)),"")</f>
         <v/>
       </c>
-      <c r="C40" s="24" t="str">
+      <c r="C40" s="29" t="str">
         <f aca="false">IFERROR(INDEX('Inventory Tracker'!$L$3:$L$52,MATCH(5,'Inventory Tracker'!$M$3:$M$52,0)),"")</f>
         <v/>
       </c>
@@ -10135,61 +10202,69 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="1" style="0" width="18"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
+    <row r="1" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A1" s="21" t="s">
         <v>110</v>
       </c>
-      <c r="B1" s="1"/>
-      <c r="C1" s="1"/>
-      <c r="D1" s="1"/>
-      <c r="E1" s="1"/>
-      <c r="F1" s="1"/>
-      <c r="G1" s="1"/>
-      <c r="H1" s="1"/>
-    </row>
-    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="4" t="s">
+      <c r="B1" s="21"/>
+      <c r="C1" s="21"/>
+      <c r="D1" s="21"/>
+      <c r="E1" s="21"/>
+      <c r="F1" s="21"/>
+      <c r="G1" s="21"/>
+      <c r="H1" s="21"/>
+    </row>
+    <row r="2" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A2" s="22" t="s">
         <v>88</v>
       </c>
-      <c r="B2" s="4"/>
-      <c r="C2" s="4"/>
-      <c r="D2" s="4"/>
-      <c r="E2" s="4"/>
-      <c r="F2" s="4"/>
-      <c r="G2" s="4"/>
-      <c r="H2" s="4"/>
-    </row>
-    <row r="5" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="21" t="s">
+      <c r="B2" s="22"/>
+      <c r="C2" s="22"/>
+      <c r="D2" s="22"/>
+      <c r="E2" s="22"/>
+      <c r="F2" s="22"/>
+      <c r="G2" s="22"/>
+      <c r="H2" s="22"/>
+    </row>
+    <row r="5" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A5" s="23" t="s">
         <v>90</v>
       </c>
-      <c r="B5" s="21" t="s">
+      <c r="B5" s="23" t="s">
         <v>111</v>
       </c>
-      <c r="C5" s="21" t="s">
+      <c r="C5" s="23" t="s">
         <v>112</v>
       </c>
-      <c r="D5" s="21" t="s">
+      <c r="D5" s="23" t="s">
         <v>113</v>
       </c>
-    </row>
-    <row r="6" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="22" t="n">
+      <c r="E5" s="24"/>
+      <c r="F5" s="24"/>
+      <c r="G5" s="24"/>
+      <c r="H5" s="24"/>
+    </row>
+    <row r="6" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A6" s="25" t="n">
         <f aca="false">COUNTA('Customer Tracker'!$B$3:$B$52)</f>
         <v>0</v>
       </c>
-      <c r="B6" s="22" t="n">
+      <c r="B6" s="25" t="n">
         <f aca="false">COUNTIFS('Customer Tracker'!$F$3:$F$52,"&gt;1")</f>
         <v>0</v>
       </c>
-      <c r="C6" s="25" t="n">
+      <c r="C6" s="30" t="n">
         <f aca="false">IFERROR(B6/A6,0)</f>
         <v>0</v>
       </c>
-      <c r="D6" s="23" t="n">
+      <c r="D6" s="26" t="n">
         <f aca="false">IFERROR(AVERAGE('Customer Tracker'!$G$3:$G$52),0)</f>
         <v>0</v>
       </c>
+      <c r="E6" s="24"/>
+      <c r="F6" s="24"/>
+      <c r="G6" s="24"/>
+      <c r="H6" s="24"/>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="6" t="s">
@@ -10197,16 +10272,16 @@
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="10" t="s">
+      <c r="A10" s="27" t="s">
         <v>109</v>
       </c>
-      <c r="B10" s="10" t="s">
+      <c r="B10" s="27" t="s">
         <v>67</v>
       </c>
-      <c r="C10" s="10" t="s">
+      <c r="C10" s="27" t="s">
         <v>115</v>
       </c>
-      <c r="D10" s="10" t="s">
+      <c r="D10" s="27" t="s">
         <v>42</v>
       </c>
     </row>
@@ -10218,7 +10293,7 @@
         <f aca="false">IFERROR(INDEX('Customer Tracker'!$B$3:$B$52,MATCH(1,'Customer Tracker'!$K$3:$K$52,0)),"")</f>
         <v/>
       </c>
-      <c r="C11" s="24" t="str">
+      <c r="C11" s="29" t="str">
         <f aca="false">IFERROR(INDEX('Customer Tracker'!$G$3:$G$52,MATCH(1,'Customer Tracker'!$K$3:$K$52,0)),"")</f>
         <v/>
       </c>
@@ -10235,7 +10310,7 @@
         <f aca="false">IFERROR(INDEX('Customer Tracker'!$B$3:$B$52,MATCH(2,'Customer Tracker'!$K$3:$K$52,0)),"")</f>
         <v/>
       </c>
-      <c r="C12" s="24" t="str">
+      <c r="C12" s="29" t="str">
         <f aca="false">IFERROR(INDEX('Customer Tracker'!$G$3:$G$52,MATCH(2,'Customer Tracker'!$K$3:$K$52,0)),"")</f>
         <v/>
       </c>
@@ -10252,7 +10327,7 @@
         <f aca="false">IFERROR(INDEX('Customer Tracker'!$B$3:$B$52,MATCH(3,'Customer Tracker'!$K$3:$K$52,0)),"")</f>
         <v/>
       </c>
-      <c r="C13" s="24" t="str">
+      <c r="C13" s="29" t="str">
         <f aca="false">IFERROR(INDEX('Customer Tracker'!$G$3:$G$52,MATCH(3,'Customer Tracker'!$K$3:$K$52,0)),"")</f>
         <v/>
       </c>
@@ -10269,7 +10344,7 @@
         <f aca="false">IFERROR(INDEX('Customer Tracker'!$B$3:$B$52,MATCH(4,'Customer Tracker'!$K$3:$K$52,0)),"")</f>
         <v/>
       </c>
-      <c r="C14" s="24" t="str">
+      <c r="C14" s="29" t="str">
         <f aca="false">IFERROR(INDEX('Customer Tracker'!$G$3:$G$52,MATCH(4,'Customer Tracker'!$K$3:$K$52,0)),"")</f>
         <v/>
       </c>
@@ -10286,7 +10361,7 @@
         <f aca="false">IFERROR(INDEX('Customer Tracker'!$B$3:$B$52,MATCH(5,'Customer Tracker'!$K$3:$K$52,0)),"")</f>
         <v/>
       </c>
-      <c r="C15" s="24" t="str">
+      <c r="C15" s="29" t="str">
         <f aca="false">IFERROR(INDEX('Customer Tracker'!$G$3:$G$52,MATCH(5,'Customer Tracker'!$K$3:$K$52,0)),"")</f>
         <v/>
       </c>
@@ -10303,7 +10378,7 @@
         <f aca="false">IFERROR(INDEX('Customer Tracker'!$B$3:$B$52,MATCH(6,'Customer Tracker'!$K$3:$K$52,0)),"")</f>
         <v/>
       </c>
-      <c r="C16" s="24" t="str">
+      <c r="C16" s="29" t="str">
         <f aca="false">IFERROR(INDEX('Customer Tracker'!$G$3:$G$52,MATCH(6,'Customer Tracker'!$K$3:$K$52,0)),"")</f>
         <v/>
       </c>
@@ -10320,7 +10395,7 @@
         <f aca="false">IFERROR(INDEX('Customer Tracker'!$B$3:$B$52,MATCH(7,'Customer Tracker'!$K$3:$K$52,0)),"")</f>
         <v/>
       </c>
-      <c r="C17" s="24" t="str">
+      <c r="C17" s="29" t="str">
         <f aca="false">IFERROR(INDEX('Customer Tracker'!$G$3:$G$52,MATCH(7,'Customer Tracker'!$K$3:$K$52,0)),"")</f>
         <v/>
       </c>
@@ -10337,7 +10412,7 @@
         <f aca="false">IFERROR(INDEX('Customer Tracker'!$B$3:$B$52,MATCH(8,'Customer Tracker'!$K$3:$K$52,0)),"")</f>
         <v/>
       </c>
-      <c r="C18" s="24" t="str">
+      <c r="C18" s="29" t="str">
         <f aca="false">IFERROR(INDEX('Customer Tracker'!$G$3:$G$52,MATCH(8,'Customer Tracker'!$K$3:$K$52,0)),"")</f>
         <v/>
       </c>
@@ -10354,7 +10429,7 @@
         <f aca="false">IFERROR(INDEX('Customer Tracker'!$B$3:$B$52,MATCH(9,'Customer Tracker'!$K$3:$K$52,0)),"")</f>
         <v/>
       </c>
-      <c r="C19" s="24" t="str">
+      <c r="C19" s="29" t="str">
         <f aca="false">IFERROR(INDEX('Customer Tracker'!$G$3:$G$52,MATCH(9,'Customer Tracker'!$K$3:$K$52,0)),"")</f>
         <v/>
       </c>
@@ -10371,7 +10446,7 @@
         <f aca="false">IFERROR(INDEX('Customer Tracker'!$B$3:$B$52,MATCH(10,'Customer Tracker'!$K$3:$K$52,0)),"")</f>
         <v/>
       </c>
-      <c r="C20" s="24" t="str">
+      <c r="C20" s="29" t="str">
         <f aca="false">IFERROR(INDEX('Customer Tracker'!$G$3:$G$52,MATCH(10,'Customer Tracker'!$K$3:$K$52,0)),"")</f>
         <v/>
       </c>
@@ -10432,7 +10507,7 @@
       <c r="A4" s="9" t="s">
         <v>119</v>
       </c>
-      <c r="B4" s="26" t="s">
+      <c r="B4" s="31" t="s">
         <v>120</v>
       </c>
     </row>
@@ -10440,7 +10515,7 @@
       <c r="A5" s="9" t="s">
         <v>121</v>
       </c>
-      <c r="B5" s="26" t="s">
+      <c r="B5" s="31" t="s">
         <v>122</v>
       </c>
     </row>
@@ -10448,7 +10523,7 @@
       <c r="A6" s="9" t="s">
         <v>123</v>
       </c>
-      <c r="B6" s="26" t="s">
+      <c r="B6" s="31" t="s">
         <v>124</v>
       </c>
     </row>
@@ -10456,7 +10531,7 @@
       <c r="A7" s="9" t="s">
         <v>125</v>
       </c>
-      <c r="B7" s="26" t="s">
+      <c r="B7" s="31" t="s">
         <v>126</v>
       </c>
     </row>
@@ -10464,7 +10539,7 @@
       <c r="A8" s="9" t="s">
         <v>127</v>
       </c>
-      <c r="B8" s="26" t="s">
+      <c r="B8" s="31" t="s">
         <v>128</v>
       </c>
     </row>
@@ -10472,7 +10547,7 @@
       <c r="A9" s="9" t="s">
         <v>129</v>
       </c>
-      <c r="B9" s="26" t="s">
+      <c r="B9" s="31" t="s">
         <v>130</v>
       </c>
     </row>
